--- a/data/trans_bre/P1401-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P1401-Clase-trans_bre.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-1,23</t>
+          <t>-1,26</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-39,93%</t>
+          <t>-39,43%</t>
         </is>
       </c>
     </row>
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,12; 3,1</t>
+          <t>0,25; 3,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 3,6</t>
+          <t>-0,05; 3,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 0,37</t>
+          <t>-3,17; 0,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -654,12 +654,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-40,36; 1176,01</t>
+          <t>-27,87; 1293,42</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-71,38; 21,33</t>
+          <t>-72,7; 18,03</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-0,38</t>
+          <t>-0,43</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-17,6%</t>
+          <t>-19,02%</t>
         </is>
       </c>
     </row>
@@ -714,22 +714,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 2,71</t>
+          <t>-0,65; 3,09</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 2,19</t>
+          <t>-1,02; 1,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 1,1</t>
+          <t>-2,1; 1,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-69,72; 869,62</t>
+          <t>-67,22; 944,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-63,36; 88,9</t>
+          <t>-64,37; 86,31</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,09</t>
+          <t>-1,08</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-4,98%</t>
+          <t>-40,43%</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 3,56</t>
+          <t>-1,2; 3,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,52; 7,78</t>
+          <t>0,51; 8,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 2,31</t>
+          <t>-2,88; 0,91</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-56,07; 229,72</t>
+          <t>-47,3; 272,09</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 1234,35</t>
+          <t>-0,46; 1247,55</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-69,01; 264,23</t>
+          <t>-82,07; 70,42</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-0,46</t>
+          <t>0,01</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-23,48%</t>
+          <t>0,78%</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 2,38</t>
+          <t>-0,53; 2,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,97</t>
+          <t>0,56; 2,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 0,55</t>
+          <t>-1,0; 0,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-45,54; 268,54</t>
+          <t>-36,38; 285,59</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>43,13; 885,78</t>
+          <t>32,58; 744,78</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-64,02; 33,88</t>
+          <t>-40,87; 62,71</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,44</t>
+          <t>1,86</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>137,98%</t>
         </is>
       </c>
     </row>
@@ -954,39 +954,39 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,42; 3,11</t>
+          <t>0,27; 3,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 2,96</t>
+          <t>-0,19; 2,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 2,6</t>
+          <t>0,66; 3,06</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11,83; 1221,75</t>
+          <t>-7,2; 1296,07</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-18,89; 357,69</t>
+          <t>-16,95; 319,4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,98; 288,46</t>
+          <t>18,83; 371,82</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2,43</t>
+          <t>2,35</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1034,17 +1034,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,41</t>
+          <t>0,14; 2,28</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,69; 1,99</t>
+          <t>0,63; 2,03</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,72; 3,39</t>
+          <t>1,67; 3,26</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>0,25</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>12,24%</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,55</t>
+          <t>0,27; 1,54</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,53; 1,78</t>
+          <t>0,54; 1,76</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 0,82</t>
+          <t>-0,31; 0,8</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18,71; 171,78</t>
+          <t>15,93; 188,58</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>46,39; 260,65</t>
+          <t>48,27; 259,87</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-19,67; 52,35</t>
+          <t>-13,2; 45,81</t>
         </is>
       </c>
     </row>
